--- a/data/trans_dic/IP44C$alquiler_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler</t>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,15</t>
+          <t>0,95; 9,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,54</t>
+          <t>0,62; 5,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,73</t>
+          <t>1,12; 5,99</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,1</t>
+          <t>0,29; 3,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,75</t>
+          <t>1,48; 6,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,88</t>
+          <t>1,13; 3,96</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,09</t>
+          <t>0,36; 2,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,36</t>
+          <t>0,9; 5,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,37</t>
+          <t>0,89; 3,2</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,86</t>
+          <t>0,47; 2,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,59</t>
+          <t>0,78; 4,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,25</t>
+          <t>0,93; 3,25</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,33</t>
+          <t>0,85; 2,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,74</t>
+          <t>1,61; 3,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,79</t>
+          <t>1,4; 2,68</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2189</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1173</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3363</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>542; 5638</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>381; 3348</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1320; 7068</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2127</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5493</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7620</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>453; 5108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2632; 10953</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3761; 13237</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6814</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>620; 4791</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1829; 10287</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3343; 11966</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3185</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6722</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9907</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1274; 7911</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2349; 14919</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5311; 18552</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>9450</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18253</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27703</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>5561; 15312</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11953; 27301</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19501; 37362</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$alquiler_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,9</t>
+          <t>0,98; 8,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,48</t>
+          <t>0,6; 5,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,99</t>
+          <t>1,14; 6,19</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,28</t>
+          <t>0,41; 3,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,15</t>
+          <t>1,31; 5,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,96</t>
+          <t>1,19; 3,94</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,82</t>
+          <t>0,25; 2,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,05</t>
+          <t>0,99; 5,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,2</t>
+          <t>0,92; 3,42</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,94</t>
+          <t>0,42; 2,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,95</t>
+          <t>0,84; 5,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,25</t>
+          <t>0,91; 3,23</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,35</t>
+          <t>0,84; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,67</t>
+          <t>1,54; 3,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,68</t>
+          <t>1,42; 2,72</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>542; 5638</t>
+          <t>557; 4905</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>381; 3348</t>
+          <t>366; 3337</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1320; 7068</t>
+          <t>1346; 7301</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>453; 5108</t>
+          <t>645; 5288</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2632; 10953</t>
+          <t>2327; 10408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3761; 13237</t>
+          <t>3961; 13172</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>620; 4791</t>
+          <t>422; 5072</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1829; 10287</t>
+          <t>2013; 10171</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3343; 11966</t>
+          <t>3443; 12780</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1274; 7911</t>
+          <t>1119; 7543</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2349; 14919</t>
+          <t>2534; 15535</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5311; 18552</t>
+          <t>5184; 18444</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5561; 15312</t>
+          <t>5503; 14974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11953; 27301</t>
+          <t>11441; 27479</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19501; 37362</t>
+          <t>19836; 37938</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$alquiler_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,61</t>
+          <t>0,56; 5,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,46</t>
+          <t>0,92; 9,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,19</t>
+          <t>1,15; 6,03</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,39</t>
+          <t>1,48; 6,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,84</t>
+          <t>0,36; 3,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,94</t>
+          <t>1,23; 4,18</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,98</t>
+          <t>0,97; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,0</t>
+          <t>0,4; 3,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,42</t>
+          <t>0,8; 3,33</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,8</t>
+          <t>0,92; 4,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,16</t>
+          <t>0,44; 2,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,23</t>
+          <t>1,04; 3,21</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,3</t>
+          <t>1,55; 3,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,69</t>
+          <t>0,87; 2,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,72</t>
+          <t>1,48; 2,84</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>884</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>2893</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>557; 4905</t>
+          <t>282; 2529</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>366; 3337</t>
+          <t>476; 5042</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1346; 7301</t>
+          <t>1175; 6138</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7047</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>645; 5288</t>
+          <t>2258; 9683</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2327; 10408</t>
+          <t>514; 4435</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3961; 13172</t>
+          <t>3654; 12394</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6589</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>422; 5072</t>
+          <t>1854; 10294</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2013; 10171</t>
+          <t>685; 5440</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3443; 12780</t>
+          <t>2915; 12081</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9907</t>
+          <t>9832</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1119; 7543</t>
+          <t>2653; 12566</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2534; 15535</t>
+          <t>1113; 7324</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5184; 18444</t>
+          <t>5616; 17277</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>17192</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27703</t>
+          <t>26362</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5503; 14974</t>
+          <t>10614; 25844</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11441; 27479</t>
+          <t>5391; 15045</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19836; 37938</t>
+          <t>19253; 36980</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$alquiler_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$alquiler_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 5,04</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,92; 9,77</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 6,03</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 6,33</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,36; 3,09</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 4,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,97; 5,37</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,4; 3,17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,8; 3,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,92; 4,36</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 2,92</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,04; 3,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 3,78</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 2,44</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 2,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.01761004728259522</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.03892308304413931</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.02841170100917131</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>884</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2893</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.005618670362421487</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.0092305418049027</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.01153823370729611</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>282; 2529</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>476; 5042</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1175; 6138</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.05036147682161769</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.0976992455264417</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.06027477352271107</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.03348708315264222</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01343742141258073</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.02378459267155692</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5120</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1927</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7047</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.01476908694565381</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.003584378107924141</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01233363248394636</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2258; 9683</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>514; 4435</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3654; 12394</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.06332335913430973</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.03093308155082558</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.04183243889523671</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.02435039925203562</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.01121889513852207</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.01814924567544608</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4665</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6589</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.009675454236793774</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.00399316245866567</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.008029971442363395</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1854; 10294</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>685; 5440</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2915; 12081</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.05372667190823815</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.0317339739136373</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.03327954202990632</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.02261609415166111</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.01321793628464568</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.01824737798420904</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>6522</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3311</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9832</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.009200195883011389</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.004445293555371992</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.01042183241769511</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2653; 12566</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1113; 7324</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>5616; 17277</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.04357656204127094</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.0292405029793778</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.03206370696955421</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.02516791528644101</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.01486395680080411</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.02027821920810732</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>17192</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>9170</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>26362</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.01553903643119006</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.008737983143996084</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.01481036645547883</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>10614; 25844</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5391; 15045</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>19253; 36980</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.03783487268015984</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.02438814627909491</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.02844623123686095</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido, al menos, algún retraso en el pago del alquiler (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>884</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>282</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>476</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2529</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>5042</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>6138</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5120</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1927</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7047</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>2258</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>514</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>3654</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>9683</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>4435</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>12394</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>4665</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1923</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>6589</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>685</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2915</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>10294</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>5440</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>12081</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>6522</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3311</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>9832</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2653</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1113</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>5616</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>12566</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>7324</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>17277</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>17192</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>9170</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>26362</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>10614</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>5391</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>19253</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>25844</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>15045</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>36980</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>